--- a/exports/510_florida.xlsx
+++ b/exports/510_florida.xlsx
@@ -1620,22 +1620,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>47560212</t>
+          <t>92567981</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BARREAL</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AMELIA</t>
+          <t>KARINA YULIETH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11/11/1992</t>
+          <t>31/07/2021</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30/08/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42071408</t>
+          <t>47560212</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BARREAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CANCHARI</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARLENI</t>
+          <t>AMELIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>04/11/1983</t>
+          <t>11/11/1992</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>30/08/2025</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>76873933</t>
+          <t>42071408</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,35 +1756,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MERCEDES</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MELVIN</t>
+          <t>MARLENI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>13/05/2005</t>
+          <t>04/11/1983</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>46026835</t>
+          <t>76873933</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MUCHA</t>
+          <t>MERCEDES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>YONY FREDY</t>
+          <t>MELVIN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01/01/1988</t>
+          <t>13/05/2005</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>63322114</t>
+          <t>46026835</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RIMACHI</t>
+          <t>MUCHA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHRISTOFER JACOB</t>
+          <t>YONY FREDY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29/10/2011</t>
+          <t>01/01/1988</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07/09/2012</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,45 +1935,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>48818004</t>
+          <t>63322114</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>RIMACHI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ALICIA</t>
+          <t>CHRISTOFER JACOB</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01/11/1990</t>
+          <t>29/10/2011</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03/10/2016</t>
+          <t>07/09/2012</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,45 +1998,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>92915419</t>
+          <t>48818004</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BLAS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KARIM TAHIR</t>
+          <t>ALICIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>31/05/2022</t>
+          <t>01/11/1990</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>27/08/2022</t>
+          <t>03/10/2016</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,45 +2061,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>48355766</t>
+          <t>92915419</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>BLAS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
+          <t>KARIM TAHIR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13/08/1994</t>
+          <t>31/05/2022</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15/03/2013</t>
+          <t>27/08/2022</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,45 +2124,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>92142090</t>
+          <t>48355766</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>YILMER AVILIO</t>
+          <t>MARICRUZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02/12/2020</t>
+          <t>13/08/1994</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>15/03/2013</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,40 +2187,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>77428457</t>
+          <t>92142090</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CALIXTO</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>YILMER AVILIO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28/09/2004</t>
+          <t>02/12/2020</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>79012460</t>
+          <t>77428457</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CALIXTO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YANDRI ARIANA</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10/03/2015</t>
+          <t>28/09/2004</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10/03/2015</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45248001</t>
+          <t>79012460</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,30 +2323,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TITO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOSE PEDRO</t>
+          <t>YANDRI ARIANA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01/05/1988</t>
+          <t>10/03/2015</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22/05/2019</t>
+          <t>10/03/2015</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09367733</t>
+          <t>45248001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CANDIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>TITO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEVERINO</t>
+          <t>JOSE PEDRO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23/01/1970</t>
+          <t>01/05/1988</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>22/05/2019</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,45 +2439,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>74963433</t>
+          <t>09367733</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CANDIA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MILAGROS LISETH</t>
+          <t>SEVERINO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31/08/1999</t>
+          <t>23/01/1970</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10/08/2025</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,45 +2502,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>25019467</t>
+          <t>74963433</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>QUINTIN OSCAR</t>
+          <t>MILAGROS LISETH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>04/11/1962</t>
+          <t>31/08/1999</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>10/08/2025</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>60102375</t>
+          <t>25019467</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CRISTIAN RICHAR</t>
+          <t>QUINTIN OSCAR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12/02/2005</t>
+          <t>04/11/1962</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>60102376</t>
+          <t>60102375</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>XIOMARA DAYANARA</t>
+          <t>CRISTIAN RICHAR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>31/08/2006</t>
+          <t>12/02/2005</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>79891791</t>
+          <t>60102376</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,30 +2706,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MAX DIEGO</t>
+          <t>XIOMARA DAYANARA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10/10/2016</t>
+          <t>31/08/2006</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10/10/2016</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>93817392</t>
+          <t>79891791</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2769,20 +2769,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AYLEN LUANA</t>
+          <t>MAX DIEGO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01/05/2024</t>
+          <t>10/10/2016</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26/05/2024</t>
+          <t>10/10/2016</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42719284</t>
+          <t>93817392</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2827,35 +2827,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RICHAR</t>
+          <t>AYLEN LUANA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28/11/1984</t>
+          <t>01/05/2024</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>26/05/2024</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>77946195</t>
+          <t>42719284</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BARBOZA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DAIKI KARIN</t>
+          <t>RICHAR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02/01/2013</t>
+          <t>28/11/1984</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06/05/2014</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>75789146</t>
+          <t>77946195</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BARBOZA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>DAIKI KARIN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,16 +2967,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13/03/2004</t>
+          <t>02/01/2013</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>06/05/2014</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>60047907</t>
+          <t>75789146</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,20 +3021,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>24/05/2006</t>
+          <t>13/03/2004</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>79514651</t>
+          <t>60047907</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3084,30 +3084,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ROMARIO</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>29/01/2016</t>
+          <t>24/05/2006</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>05/04/2016</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>91698640</t>
+          <t>79514651</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAYDA</t>
+          <t>ROMARIO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>26/01/2020</t>
+          <t>29/01/2016</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>26/01/2025</t>
+          <t>05/04/2016</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28591667</t>
+          <t>91698640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3205,30 +3205,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AQUILES</t>
+          <t>SAYDA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>07/11/1950</t>
+          <t>26/01/2020</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>26/01/2025</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>79228663</t>
+          <t>28591667</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AREM RICARDO</t>
+          <t>AQUILES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>04/08/2015</t>
+          <t>07/11/1950</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>04/08/2015</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>92611665</t>
+          <t>79228663</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ADRIEL</t>
+          <t>AREM RICARDO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>04/11/2021</t>
+          <t>04/08/2015</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>10/01/2023</t>
+          <t>04/08/2015</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>45040747</t>
+          <t>92611665</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NELSON</t>
+          <t>ADRIEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>09/05/1988</t>
+          <t>04/11/2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>10/01/2023</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23969574</t>
+          <t>45040747</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>POTOCINO</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>NELSON</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,11 +3471,11 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/04/1973</t>
+          <t>09/05/1988</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49070415</t>
+          <t>23969574</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VILLAR</t>
+          <t>POTOCINO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>07/04/1991</t>
+          <t>18/04/1973</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>07/09/2022</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,45 +3573,45 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>62269253</t>
+          <t>49070415</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CCORIPURI</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>VILLAR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NICOL MELODI</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02/03/2007</t>
+          <t>07/04/1991</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>07/09/2022</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>62094257</t>
+          <t>62269253</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>QUITLIS SEFER</t>
+          <t>NICOL MELODI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01/02/2010</t>
+          <t>02/03/2007</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28576582</t>
+          <t>62094257</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JUAN ARCADIO</t>
+          <t>QUITLIS SEFER</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12/01/1969</t>
+          <t>01/02/2010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28527042</t>
+          <t>28576582</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ZENOBIA</t>
+          <t>JUAN ARCADIO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14/02/1977</t>
+          <t>12/01/1969</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42758477</t>
+          <t>28527042</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,20 +3840,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EDWIN</t>
+          <t>ZENOBIA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>26/10/1984</t>
+          <t>14/02/1977</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>45930796</t>
+          <t>42758477</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SEBERO EFRIN</t>
+          <t>EDWIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01/02/1987</t>
+          <t>26/10/1984</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>60148327</t>
+          <t>45930796</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JHOAN KENNY</t>
+          <t>SEBERO EFRIN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19/11/2006</t>
+          <t>01/02/1987</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>81392343</t>
+          <t>60148327</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JHINO EYAL</t>
+          <t>JHOAN KENNY</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20/04/2014</t>
+          <t>19/11/2006</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>25/07/2016</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>91369531</t>
+          <t>81392343</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,30 +4087,30 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CAMILA YOSSI</t>
+          <t>JHINO EYAL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14/06/2019</t>
+          <t>20/04/2014</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>14/06/2024</t>
+          <t>25/07/2016</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,40 +4140,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>48827459</t>
+          <t>91369531</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>CCORIPURI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SERENA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ALCIDES</t>
+          <t>CAMILA YOSSI</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14/05/1990</t>
+          <t>14/06/2019</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/03/2015</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>63322116</t>
+          <t>48827459</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,25 +4218,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AYDEE</t>
+          <t>ALCIDES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>30/04/1997</t>
+          <t>14/05/1990</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>23/03/2020</t>
+          <t>31/03/2015</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>63322082</t>
+          <t>63322116</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SILVERA</t>
+          <t>SERENA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ANALI</t>
+          <t>AYDEE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15/06/2011</t>
+          <t>30/04/1997</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/03/2015</t>
+          <t>23/03/2020</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>77292149</t>
+          <t>63322082</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>SILVERA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JHESENIA ARASELY</t>
+          <t>ANALI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>08/03/2006</t>
+          <t>15/06/2011</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>31/03/2015</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>28529642</t>
+          <t>77292149</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4402,35 +4402,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PEÑAFIEL</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ZOCIMO</t>
+          <t>JHESENIA ARASELY</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>01/04/1969</t>
+          <t>08/03/2006</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,40 +4455,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>91369457</t>
+          <t>28529642</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CHACHAYMA</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>PEÑAFIEL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EDITH ABIGAIL</t>
+          <t>ZOCIMO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14/06/2019</t>
+          <t>01/04/1969</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14/06/2024</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>81952232</t>
+          <t>91369457</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CHAICO</t>
+          <t>CHACHAYMA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MAJHY IMASUMACC</t>
+          <t>EDITH ABIGAIL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10/07/2021</t>
+          <t>14/06/2019</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06940947</t>
+          <t>81952232</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CHAICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MARTHA SATURNINA</t>
+          <t>MAJHY IMASUMACC</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/01/1965</t>
+          <t>10/07/2021</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>78251205</t>
+          <t>06940947</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ROUS ANALY</t>
+          <t>MARTHA SATURNINA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,16 +4668,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10/09/2013</t>
+          <t>19/01/1965</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/09/2013</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>60514768</t>
+          <t>78251205</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CHIMAYCO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>ROUS ANALY</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/10/1995</t>
+          <t>10/09/2013</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>30/09/2013</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>60514770</t>
+          <t>60514768</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MICHAEL</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,16 +4794,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14/12/1998</t>
+          <t>17/10/1995</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>60514769</t>
+          <t>60514770</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ROYER</t>
+          <t>MICHAEL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13/02/2001</t>
+          <t>14/12/1998</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>76876687</t>
+          <t>60514769</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4911,20 +4911,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>GLIONILDA</t>
+          <t>ROYER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12/09/2004</t>
+          <t>13/02/2001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>61879286</t>
+          <t>76876687</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RAQUEL ZARAI</t>
+          <t>GLIONILDA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20/07/2009</t>
+          <t>12/09/2004</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>42948912</t>
+          <t>61879286</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CIERTO</t>
+          <t>CHIMAYCO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>RAQUEL ZARAI</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,21 +5046,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28/03/1985</t>
+          <t>20/07/2009</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>04/10/2022</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,45 +5085,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28564778</t>
+          <t>42948912</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CIERTO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>04/05/1954</t>
+          <t>28/03/1985</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>04/10/2022</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28527473</t>
+          <t>28564778</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10/03/1975</t>
+          <t>04/05/1954</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>42420496</t>
+          <t>28527473</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ABDON</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>08/04/1980</t>
+          <t>10/03/1975</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>44951196</t>
+          <t>42420496</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5284,25 +5284,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>ABDON</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>15/06/1985</t>
+          <t>08/04/1980</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>44120368</t>
+          <t>44951196</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RUTH MARIBEL</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,11 +5361,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>02/12/1986</t>
+          <t>15/06/1985</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>46291698</t>
+          <t>44120368</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EDITA</t>
+          <t>RUTH MARIBEL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>16/10/1989</t>
+          <t>02/12/1986</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>70918288</t>
+          <t>46291698</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5478,20 +5478,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>HUBER</t>
+          <t>EDITA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>27/02/1993</t>
+          <t>16/10/1989</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18/10/2018</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>79476788</t>
+          <t>70918288</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5536,35 +5536,35 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LUCIA SHERYL</t>
+          <t>HUBER</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14/01/2016</t>
+          <t>27/02/1993</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>18/10/2018</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>94339353</t>
+          <t>79476788</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AMBER THAIZ</t>
+          <t>LUCIA SHERYL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>14/01/2016</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>70419395</t>
+          <t>94339353</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>AMBER THAIZ</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>03/04/1992</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>10/07/2018</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>43875546</t>
+          <t>70419395</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BEKY MIRIELA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>02/02/1984</t>
+          <t>03/04/1992</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>10/07/2018</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>76878694</t>
+          <t>43875546</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5788,25 +5788,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ROY</t>
+          <t>BEKY MIRIELA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>22/04/1995</t>
+          <t>02/02/1984</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>81780144</t>
+          <t>76878694</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>JHEFERSON</t>
+          <t>ROY</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>22/11/2019</t>
+          <t>22/04/1995</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,35 +5904,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>79436199</t>
+          <t>81780144</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AZUMI</t>
+          <t>JHEFERSON</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>15/08/2015</t>
+          <t>22/11/2019</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>19/04/2016</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>43252782</t>
+          <t>79436199</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ERCILIA</t>
+          <t>AZUMI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,16 +5991,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>30/10/1985</t>
+          <t>15/08/2015</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>19/04/2016</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>48741177</t>
+          <t>43252782</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6045,20 +6045,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>ERCILIA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23/12/1990</t>
+          <t>30/10/1985</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>70934022</t>
+          <t>48741177</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MILTON</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,11 +6117,11 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01/09/1995</t>
+          <t>23/12/1990</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>28/08/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>90636443</t>
+          <t>70934022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6166,30 +6166,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SOLIER</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AYLEN ITZEL</t>
+          <t>MILTON</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19/02/2018</t>
+          <t>01/09/1995</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>19/02/2023</t>
+          <t>28/08/2012</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>94447401</t>
+          <t>90636443</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>YARETZI AITHANA</t>
+          <t>AYLEN ITZEL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>19/02/2018</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>19/02/2023</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>45349083</t>
+          <t>94447401</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CUSICHE</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>SOLIER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>YARETZI AITHANA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>12/03/1986</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>91595794</t>
+          <t>45349083</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>RONY ANGELO</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,21 +6369,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>17/11/2019</t>
+          <t>12/03/1986</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,40 +6408,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>28597855</t>
+          <t>91595794</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CUSICHE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>RONY ANGELO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>09/11/1971</t>
+          <t>17/11/2019</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>04/05/2014</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>28278800</t>
+          <t>28597855</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>27/07/1968</t>
+          <t>09/11/1971</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>28/06/2013</t>
+          <t>04/05/2014</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,35 +6534,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>47062994</t>
+          <t>28278800</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PAREJAS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>29/09/1987</t>
+          <t>27/07/1968</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>23/05/2018</t>
+          <t>28/06/2013</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,27 +6597,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>45040752</t>
+          <t>47062994</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>PAREJAS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JANETH GLADYS</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>07/09/1987</t>
+          <t>29/09/1987</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>23/05/2018</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>28575953</t>
+          <t>45040752</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6670,25 +6670,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>REYMUNDO</t>
+          <t>JANETH GLADYS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>15/03/1968</t>
+          <t>07/09/1987</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>90165979</t>
+          <t>28575953</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LIAM SMITH</t>
+          <t>REYMUNDO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>09/04/2017</t>
+          <t>15/03/1968</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>21/05/2022</t>
+          <t>01/06/2015</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,35 +6786,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>94568193</t>
+          <t>90165979</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>YAMILET SHANTAL</t>
+          <t>LIAM SMITH</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>09/04/2017</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>21/05/2022</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,22 +6849,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>80424659</t>
+          <t>94568193</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GAVILAN</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MAXIMINA</t>
+          <t>YAMILET SHANTAL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>13/04/1970</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>90449180</t>
+          <t>80424659</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ASTUPILLO</t>
+          <t>GAVILAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>HAIME STELA</t>
+          <t>MAXIMINA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15/10/2017</t>
+          <t>13/04/1970</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>15/10/2022</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,7 +6975,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>91648713</t>
+          <t>90449180</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CCENCHO</t>
+          <t>ASTUPILLO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PRISCILA LOURDES</t>
+          <t>HAIME STELA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,11 +6999,11 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>23/12/2019</t>
+          <t>15/10/2017</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>23/12/2024</t>
+          <t>15/10/2022</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>74349616</t>
+          <t>91648713</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7048,30 +7048,30 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>CCENCHO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>JHONATAN</t>
+          <t>PRISCILA LOURDES</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>31/12/1994</t>
+          <t>23/12/2019</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>23/12/2024</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>74349617</t>
+          <t>74349616</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>JHONATAN</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>30/11/1996</t>
+          <t>31/12/1994</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>63433394</t>
+          <t>74349617</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>01/02/1999</t>
+          <t>30/11/1996</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>77800813</t>
+          <t>63433394</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BRICH MILANDER</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>01/11/2003</t>
+          <t>01/02/1999</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>77916546</t>
+          <t>77800813</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7305,20 +7305,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>KAREN NATALY</t>
+          <t>BRICH MILANDER</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>10/12/2005</t>
+          <t>01/11/2003</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>60240738</t>
+          <t>77916546</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7368,20 +7368,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>KENYO EUSEBIO</t>
+          <t>KAREN NATALY</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>03/11/2007</t>
+          <t>10/12/2005</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>63339068</t>
+          <t>60240738</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ALDO ALEXIS</t>
+          <t>KENYO EUSEBIO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>24/04/2011</t>
+          <t>03/11/2007</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>79413404</t>
+          <t>63339068</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7494,30 +7494,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SELA NAREEN</t>
+          <t>ALDO ALEXIS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>04/12/2015</t>
+          <t>24/04/2011</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>05/12/2015</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,7 +7542,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>91363295</t>
+          <t>79413404</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VALENTINA KAREN</t>
+          <t>SELA NAREEN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7566,11 +7566,11 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10/06/2019</t>
+          <t>04/12/2015</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>10/06/2024</t>
+          <t>05/12/2015</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,7 +7605,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>62473413</t>
+          <t>91363295</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7615,30 +7615,30 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
+          <t>VALENTINA KAREN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>16/09/2005</t>
+          <t>10/06/2019</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>81780143</t>
+          <t>62473413</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SAMAMPO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DEYVI</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>19/11/2019</t>
+          <t>16/09/2005</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>19/11/2024</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,7 +7731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>25008275</t>
+          <t>81780143</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>SAMAMPO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EUSEBIO</t>
+          <t>DEYVI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>01/08/1957</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>19/11/2024</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,40 +7794,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01189752</t>
+          <t>25008275</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AQUINO</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ROSALBA</t>
+          <t>EUSEBIO</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>19/11/1977</t>
+          <t>01/08/1957</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>15/06/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,40 +7857,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>91820447</t>
+          <t>01189752</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t>FONSECA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ANCCASI</t>
+          <t>AQUINO</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JAMIR ABDIEL</t>
+          <t>ROSALBA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>19/04/2020</t>
+          <t>19/11/1977</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>19/04/2025</t>
+          <t>15/06/2012</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>46500135</t>
+          <t>91820447</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7930,30 +7930,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CONDORAY</t>
+          <t>ANCCASI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LURGIA</t>
+          <t>JAMIR ABDIEL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>24/08/1990</t>
+          <t>19/04/2020</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>19/04/2025</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,35 +7983,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>23258707</t>
+          <t>46500135</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GAMBOA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>CONDORAY</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NARCISO</t>
+          <t>LURGIA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>15/04/1976</t>
+          <t>24/08/1990</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,45 +8046,45 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>91610005</t>
+          <t>23258707</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ANALY AMARA</t>
+          <t>NARCISO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>26/11/2019</t>
+          <t>15/04/1976</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,40 +8109,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>41790369</t>
+          <t>91610005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SINARAHUA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SEGUNDO JUAN</t>
+          <t>ANALY AMARA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>17/03/1982</t>
+          <t>26/11/2019</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>27/05/2015</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,22 +8172,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>48406841</t>
+          <t>41790369</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JAULIS</t>
+          <t>SINARAHUA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8196,11 +8196,11 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23/09/1986</t>
+          <t>17/03/1982</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>27/05/2015</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>62227456</t>
+          <t>48406841</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8245,35 +8245,35 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>JAULIS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DARA ROUSE</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>22/09/2010</t>
+          <t>23/09/1986</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,35 +8298,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>81583934</t>
+          <t>62227456</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LIAN ANTONIO</t>
+          <t>DARA ROUSE</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>07/05/2014</t>
+          <t>22/09/2010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>23/09/2018</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,7 +8361,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>91741583</t>
+          <t>81583934</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8376,30 +8376,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ABIGAIL NAISHA</t>
+          <t>LIAN ANTONIO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22/02/2020</t>
+          <t>07/05/2014</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>22/02/2025</t>
+          <t>23/09/2018</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,7 +8424,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>45768669</t>
+          <t>91741583</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8434,30 +8434,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NELSON</t>
+          <t>ABIGAIL NAISHA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>21/06/1989</t>
+          <t>22/02/2020</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>20/08/2012</t>
+          <t>22/02/2025</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,35 +8487,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>80091710</t>
+          <t>45768669</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CAMASI</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>NELSON</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>15/08/1976</t>
+          <t>21/06/1989</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>20/08/2012</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>93269447</t>
+          <t>80091710</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LUNAZCO</t>
+          <t>CAMASI</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>KHIARA BELEN</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,21 +8574,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>18/02/2023</t>
+          <t>15/08/1976</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>13/03/2023</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>91934044</t>
+          <t>93269447</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MANUELO</t>
+          <t>LUNAZCO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>YEIRA ZAMARA</t>
+          <t>KHIARA BELEN</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,11 +8637,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>04/07/2020</t>
+          <t>18/02/2023</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>13/03/2023</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>94420538</t>
+          <t>91934044</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>JAZLIN AITANA</t>
+          <t>YEIRA ZAMARA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,11 +8700,11 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>04/07/2020</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>28282421</t>
+          <t>94420538</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,35 +8749,35 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>MANUELO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>HUMBERTO</t>
+          <t>JAZLIN AITANA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>24/07/1945</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>76088573</t>
+          <t>28282421</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,35 +8812,35 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>YUDITH</t>
+          <t>HUMBERTO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>01/04/1995</t>
+          <t>24/07/1945</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,7 +8865,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>81623248</t>
+          <t>76088573</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8880,30 +8880,30 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>JOSEPH</t>
+          <t>YUDITH</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>08/04/2015</t>
+          <t>01/04/1995</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>30/10/2015</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,40 +8928,40 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>28567493</t>
+          <t>81623248</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ODILIA</t>
+          <t>JOSEPH</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>05/10/1965</t>
+          <t>08/04/2015</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>14/09/2011</t>
+          <t>30/10/2015</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,7 +8991,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>28595773</t>
+          <t>28567493</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OLGA</t>
+          <t>ODILIA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>28/12/1968</t>
+          <t>05/10/1965</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>14/09/2011</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>28529650</t>
+          <t>28595773</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>MARUJA</t>
+          <t>OLGA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>18/10/1973</t>
+          <t>28/12/1968</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9117,7 +9117,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>60148332</t>
+          <t>28529650</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9127,25 +9127,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>MARUJA</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21/11/1994</t>
+          <t>18/10/1973</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>23/09/2018</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,7 +9180,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>62227494</t>
+          <t>60148332</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9195,30 +9195,30 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>MARILY</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>25/08/1997</t>
+          <t>21/11/1994</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>23/09/2018</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>62227253</t>
+          <t>62227494</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SADITH ANGELA</t>
+          <t>MARILY</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>17/05/1999</t>
+          <t>25/08/1997</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,45 +9306,45 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>23214772</t>
+          <t>62227253</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HUIZA</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ELVES</t>
+          <t>SADITH ANGELA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>19/10/1974</t>
+          <t>17/05/1999</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,22 +9369,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>06167167</t>
+          <t>23214772</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>HUIZA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIONICIO</t>
+          <t>ELVES</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>08/04/1962</t>
+          <t>19/10/1974</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>28/06/2013</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,22 +9432,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>42529614</t>
+          <t>06167167</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LAMARTINO</t>
+          <t>DIONICIO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9456,16 +9456,16 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>17/02/1983</t>
+          <t>08/04/1962</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>28/06/2013</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>40965309</t>
+          <t>42529614</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ROSARIO</t>
+          <t>LAMARTINO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>09/08/1981</t>
+          <t>17/02/1983</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,22 +9558,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>28315335</t>
+          <t>40965309</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JUSCAMAYTA</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CCORAHUA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>ROSARIO</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9582,11 +9582,11 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22/01/1975</t>
+          <t>09/08/1981</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>94206134</t>
+          <t>28315335</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CCORAHUA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>TAYLOR LEONEL</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>22/01/1975</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>76878775</t>
+          <t>94206134</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ROY EDILBERTO</t>
+          <t>TAYLOR LEONEL</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,21 +9708,21 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>22/10/1999</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>91128790</t>
+          <t>76878775</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>JUSCAMAYTA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>BERTA ELOISA</t>
+          <t>ROY EDILBERTO</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>16/10/2006</t>
+          <t>22/10/1999</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>30/12/2020</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,45 +9810,45 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>92880446</t>
+          <t>91128790</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>EMIR KENNETH</t>
+          <t>BERTA ELOISA</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>07/05/2022</t>
+          <t>16/10/2006</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,22 +9873,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>91045162</t>
+          <t>92880446</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LIFONCIO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>THIAGO AYRTON</t>
+          <t>EMIR KENNETH</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9897,11 +9897,11 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>10/10/2018</t>
+          <t>07/05/2022</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>10/10/2023</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,7 +9936,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>92986471</t>
+          <t>91045162</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PORMACHI</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>IAN JAZIEL</t>
+          <t>THIAGO AYRTON</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22/07/2022</t>
+          <t>10/10/2018</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>22/09/2022</t>
+          <t>10/10/2023</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,22 +9999,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>91595902</t>
+          <t>92986471</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LIFONCIO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>PORMACHI</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ERICK SUNYU</t>
+          <t>IAN JAZIEL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10023,11 +10023,11 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>17/11/2019</t>
+          <t>22/07/2022</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>22/09/2022</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,7 +10062,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>41002505</t>
+          <t>91595902</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10072,30 +10072,30 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>BASILIA</t>
+          <t>ERICK SUNYU</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>04/04/1976</t>
+          <t>17/11/2019</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,22 +10125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>91606830</t>
+          <t>41002505</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LUANA ESPERANZA</t>
+          <t>BASILIA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10149,16 +10149,16 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>24/11/2019</t>
+          <t>04/04/1976</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>24/11/2024</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,7 +10188,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>70793406</t>
+          <t>91606830</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AYDA LUZ</t>
+          <t>LUANA ESPERANZA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10212,16 +10212,16 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>10/02/1994</t>
+          <t>24/11/2019</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>10/09/2012</t>
+          <t>24/11/2024</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,35 +10251,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>70419413</t>
+          <t>70793406</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>AYDA LUZ</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>03/11/1991</t>
+          <t>10/02/1994</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>10/09/2012</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>90739428</t>
+          <t>70419413</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AXEL GAEL VEKER</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10338,21 +10338,21 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22/04/2018</t>
+          <t>03/11/1991</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>22/04/2023</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,40 +10377,40 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>46743091</t>
+          <t>90739428</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>MARUJA</t>
+          <t>AXEL GAEL VEKER</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>29/12/1990</t>
+          <t>22/04/2018</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>22/04/2023</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,7 +10440,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>91610034</t>
+          <t>46743091</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ZAMBRANO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>JENNIFER CAMILA</t>
+          <t>MARUJA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10464,16 +10464,16 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>26/11/2019</t>
+          <t>29/12/1990</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,27 +10503,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>91502056</t>
+          <t>91610034</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CUYA</t>
+          <t>ZAMBRANO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DERECK CALE</t>
+          <t>JENNIFER CAMILA</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>15/09/2019</t>
+          <t>26/11/2019</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>74098389</t>
+          <t>91502056</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUJAN</t>
+          <t>LUERA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>CUYA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>GABRIEL SHEROO</t>
+          <t>DERECK CALE</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>19/03/2009</t>
+          <t>15/09/2019</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>71671966</t>
+          <t>74098389</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>LUJAN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SILVERA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ANGEL JOEL</t>
+          <t>GABRIEL SHEROO</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,21 +10653,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>27/05/2008</t>
+          <t>19/03/2009</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10692,22 +10692,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>94044801</t>
+          <t>71671966</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUNASCO</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SILVERA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>EITAN MATEO</t>
+          <t>ANGEL JOEL</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>27/05/2008</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10755,35 +10755,35 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>91387361</t>
+          <t>94044801</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MADUEÑO</t>
+          <t>LUNASCO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LUZ JHANDIRA</t>
+          <t>EITAN MATEO</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>26/06/2019</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>26/06/2024</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10818,40 +10818,40 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>40796044</t>
+          <t>91387361</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MALLMA</t>
+          <t>MADUEÑO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LUZ JHANDIRA</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>19/04/1980</t>
+          <t>26/06/2019</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>21/10/2011</t>
+          <t>26/06/2024</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10881,7 +10881,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>60240717</t>
+          <t>40796044</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>POTOSINO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>JUAN ANDREE</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>15/06/2007</t>
+          <t>19/04/1980</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10944,7 +10944,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>28586274</t>
+          <t>60240717</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>VICAÑA</t>
+          <t>POTOSINO</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NICANOR</t>
+          <t>JUAN ANDREE</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>10/01/1961</t>
+          <t>15/06/2007</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>03/11/2011</t>
+          <t>21/10/2011</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11007,22 +11007,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>28586517</t>
+          <t>28586274</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MALLQUI</t>
+          <t>MALLMA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CRESPO</t>
+          <t>VICAÑA</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>NICANOR</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11031,11 +11031,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>15/07/1952</t>
+          <t>10/01/1961</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/11/2011</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11070,45 +11070,45 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>93204094</t>
+          <t>28586517</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>MALLQUI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>POTOSINO</t>
+          <t>CRESPO</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SOFIA ALEJANDRA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>03/01/2023</t>
+          <t>15/07/1952</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>03/07/2023</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11133,45 +11133,45 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>48366775</t>
+          <t>93204094</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MANUELO</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>JULIAN</t>
+          <t>POTOSINO</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ELVIS MAYCO</t>
+          <t>SOFIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>07/10/1993</t>
+          <t>03/01/2023</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>03/07/2023</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11196,7 +11196,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>80713430</t>
+          <t>48366775</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11206,35 +11206,35 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>JULIAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ALEJANDRA JIMENA</t>
+          <t>ELVIS MAYCO</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>24/08/2012</t>
+          <t>07/10/1993</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11259,22 +11259,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>61578090</t>
+          <t>80713430</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MANUELO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CIERTO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ANYELA YESMILINDA</t>
+          <t>ALEJANDRA JIMENA</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11283,11 +11283,11 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22/02/2010</t>
+          <t>24/08/2012</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11322,7 +11322,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>81227078</t>
+          <t>61578090</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11337,20 +11337,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>MIULLER NEYMAR</t>
+          <t>ANYELA YESMILINDA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20/05/2013</t>
+          <t>22/02/2010</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>42635312</t>
+          <t>81227078</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CIERTO</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t>MIULLER NEYMAR</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11409,16 +11409,16 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>05/01/1983</t>
+          <t>20/05/2013</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>21/10/2022</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11448,7 +11448,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>42811694</t>
+          <t>42635312</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>CORNELIO MEUJAEL</t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11472,11 +11472,11 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20/01/1985</t>
+          <t>05/01/1983</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>21/10/2022</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11511,45 +11511,45 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>60658354</t>
+          <t>42811694</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>EDITH SOLANCH</t>
+          <t>CORNELIO MEUJAEL</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>01/11/2007</t>
+          <t>20/01/1985</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11574,22 +11574,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>41037974</t>
+          <t>60658354</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SINCHITULLO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NORA ENMA</t>
+          <t>EDITH SOLANCH</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11598,21 +11598,21 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>01/07/1981</t>
+          <t>01/11/2007</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11637,35 +11637,35 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>46542581</t>
+          <t>41037974</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CAYETANO</t>
+          <t>SINCHITULLO</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>NORA ENMA</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>30/11/1986</t>
+          <t>01/07/1981</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11700,7 +11700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>62227255</t>
+          <t>46542581</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11724,16 +11724,16 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>08/09/1998</t>
+          <t>30/11/1986</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11763,7 +11763,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>60537115</t>
+          <t>62227255</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CAYETANO</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>JOSEPH ELEOSSER</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11787,11 +11787,11 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>24/07/2007</t>
+          <t>08/09/1998</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>93524537</t>
+          <t>60537115</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>JHANDIEL ENZO</t>
+          <t>JOSEPH ELEOSSER</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11850,21 +11850,21 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>24/07/2007</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>93717006</t>
+          <t>93524537</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11899,25 +11899,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>VICAÑA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KORAL ITSAYANA</t>
+          <t>JHANDIEL ENZO</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>10/02/2024</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>08/05/2024</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11952,22 +11952,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>28587451</t>
+          <t>93717006</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>VICAÑA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NANCIA</t>
+          <t>KORAL ITSAYANA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11976,21 +11976,21 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>12/04/1968</t>
+          <t>10/02/2024</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12015,22 +12015,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>28570376</t>
+          <t>28587451</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>MERCEDES TOMASA</t>
+          <t>NANCIA</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12039,21 +12039,21 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>24/12/1944</t>
+          <t>12/04/1968</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12078,40 +12078,40 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>42110156</t>
+          <t>28570376</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OBREGON</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>MERCEDES TOMASA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>13/07/1981</t>
+          <t>24/12/1944</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12141,7 +12141,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>70325895</t>
+          <t>42110156</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>FELIMON ABRAHAM</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12165,11 +12165,11 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>15/04/1989</t>
+          <t>13/07/1981</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>08/09/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>78027451</t>
+          <t>70325895</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12214,35 +12214,35 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SAMMY</t>
+          <t>FELIMON ABRAHAM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>04/02/2013</t>
+          <t>15/04/1989</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>27/05/2015</t>
+          <t>08/09/2012</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>79603222</t>
+          <t>78027451</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12282,30 +12282,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ERICK YANDEL</t>
+          <t>SAMMY</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>04/04/2016</t>
+          <t>04/02/2013</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>04/04/2016</t>
+          <t>27/05/2015</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12330,7 +12330,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>93229578</t>
+          <t>79603222</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>GAEL LUDWIN</t>
+          <t>ERICK YANDEL</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12354,11 +12354,11 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>21/01/2023</t>
+          <t>04/04/2016</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>21/01/2023</t>
+          <t>04/04/2016</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12393,22 +12393,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>28563981</t>
+          <t>93229578</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>OBREGON</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>GAEL LUDWIN</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12417,21 +12417,21 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>18/01/1965</t>
+          <t>21/01/2023</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>21/01/2023</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>60514862</t>
+          <t>28563981</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12466,35 +12466,35 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SERENA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>16/03/2004</t>
+          <t>18/01/1965</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12519,45 +12519,45 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>47365956</t>
+          <t>60514862</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SERENA</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NOE GABRIEL</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>03/04/1984</t>
+          <t>16/03/2004</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12582,7 +12582,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>77352851</t>
+          <t>47365956</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12592,12 +12592,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>GABRIEL URBANO</t>
+          <t>NOE GABRIEL</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12606,16 +12606,16 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>26/03/2001</t>
+          <t>03/04/1984</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12645,7 +12645,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>76876706</t>
+          <t>77352851</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>KERVIN EDWARD</t>
+          <t>GABRIEL URBANO</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12669,11 +12669,11 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>18/04/2003</t>
+          <t>26/03/2001</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>76874672</t>
+          <t>76876706</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>JUNIOR DEYVIS</t>
+          <t>KERVIN EDWARD</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12732,11 +12732,11 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>19/06/2005</t>
+          <t>18/04/2003</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12771,7 +12771,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>62473415</t>
+          <t>76874672</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12786,25 +12786,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>YUREMA</t>
+          <t>JUNIOR DEYVIS</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>16/01/2009</t>
+          <t>19/06/2005</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12834,7 +12834,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>63322117</t>
+          <t>62473415</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>YUNGA ZAURI</t>
+          <t>YUREMA</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12858,11 +12858,11 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>26/08/2011</t>
+          <t>16/01/2009</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12897,40 +12897,40 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>76254509</t>
+          <t>63322117</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>JOSE ANDRES</t>
+          <t>YUNGA ZAURI</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>31/05/2005</t>
+          <t>26/08/2011</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">

--- a/exports/510_florida.xlsx
+++ b/exports/510_florida.xlsx
@@ -1620,22 +1620,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>92567981</t>
+          <t>47560212</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>BARREAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KARINA YULIETH</t>
+          <t>AMELIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>31/07/2021</t>
+          <t>11/11/1992</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>30/08/2025</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1683,22 +1683,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>47560212</t>
+          <t>42071408</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BARREAL</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AMELIA</t>
+          <t>MARLENI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11/11/1992</t>
+          <t>04/11/1983</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30/08/2025</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42071408</t>
+          <t>76873933</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,35 +1756,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CANCHARI</t>
+          <t>MERCEDES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARLENI</t>
+          <t>MELVIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>04/11/1983</t>
+          <t>13/05/2005</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>76873933</t>
+          <t>46026835</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MERCEDES</t>
+          <t>MUCHA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MELVIN</t>
+          <t>YONY FREDY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13/05/2005</t>
+          <t>01/01/1988</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46026835</t>
+          <t>63322114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MUCHA</t>
+          <t>RIMACHI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>YONY FREDY</t>
+          <t>CHRISTOFER JACOB</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01/01/1988</t>
+          <t>29/10/2011</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>07/09/2012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1935,45 +1935,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>63322114</t>
+          <t>48818004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RIMACHI</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHRISTOFER JACOB</t>
+          <t>ALICIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/10/2011</t>
+          <t>01/11/1990</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>07/09/2012</t>
+          <t>03/10/2016</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,45 +1998,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>48818004</t>
+          <t>92915419</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>BLAS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALICIA</t>
+          <t>KARIM TAHIR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01/11/1990</t>
+          <t>31/05/2022</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03/10/2016</t>
+          <t>27/08/2022</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,45 +2061,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>92915419</t>
+          <t>48355766</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BLAS</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KARIM TAHIR</t>
+          <t>MARICRUZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31/05/2022</t>
+          <t>13/08/1994</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27/08/2022</t>
+          <t>15/03/2013</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,45 +2124,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>48355766</t>
+          <t>92142090</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MARICRUZ</t>
+          <t>YILMER AVILIO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>13/08/1994</t>
+          <t>02/12/2020</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15/03/2013</t>
+          <t>29/12/2025</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,40 +2187,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>92142090</t>
+          <t>77428457</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CALIXTO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YILMER AVILIO</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02/12/2020</t>
+          <t>28/09/2004</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>29/12/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,22 +2250,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>77428457</t>
+          <t>79012460</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CALIXTO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>YANDRI ARIANA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28/09/2004</t>
+          <t>10/03/2015</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>10/03/2015</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>79012460</t>
+          <t>45248001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,30 +2323,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>TITO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>YANDRI ARIANA</t>
+          <t>JOSE PEDRO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10/03/2015</t>
+          <t>01/05/1988</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10/03/2015</t>
+          <t>22/05/2019</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45248001</t>
+          <t>09367733</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANDIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TITO</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE PEDRO</t>
+          <t>SEVERINO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,11 +2400,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01/05/1988</t>
+          <t>23/01/1970</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22/05/2019</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,45 +2439,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09367733</t>
+          <t>74963433</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CANDIA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEVERINO</t>
+          <t>MILAGROS LISETH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23/01/1970</t>
+          <t>31/08/1999</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>10/08/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,45 +2502,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>74963433</t>
+          <t>25019467</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CARPIO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MILAGROS LISETH</t>
+          <t>QUINTIN OSCAR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>31/08/1999</t>
+          <t>04/11/1962</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>10/08/2025</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25019467</t>
+          <t>60102375</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CARPIO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>QUINTIN OSCAR</t>
+          <t>CRISTIAN RICHAR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>04/11/1962</t>
+          <t>12/02/2005</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>60102375</t>
+          <t>60102376</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CRISTIAN RICHAR</t>
+          <t>XIOMARA DAYANARA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12/02/2005</t>
+          <t>31/08/2006</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>60102376</t>
+          <t>79891791</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,30 +2706,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>XIOMARA DAYANARA</t>
+          <t>MAX DIEGO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31/08/2006</t>
+          <t>10/10/2016</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>10/10/2016</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>79891791</t>
+          <t>93817392</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2769,20 +2769,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MAX DIEGO</t>
+          <t>AYLEN LUANA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10/10/2016</t>
+          <t>01/05/2024</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10/10/2016</t>
+          <t>26/05/2024</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>93817392</t>
+          <t>42719284</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2827,35 +2827,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AYLEN LUANA</t>
+          <t>RICHAR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01/05/2024</t>
+          <t>28/11/1984</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>26/05/2024</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,22 +2880,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42719284</t>
+          <t>77946195</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CCENTE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>BARBOZA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RICHAR</t>
+          <t>DAIKI KARIN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28/11/1984</t>
+          <t>02/01/2013</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>06/05/2014</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>77946195</t>
+          <t>75789146</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BARBOZA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DAIKI KARIN</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,16 +2967,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>02/01/2013</t>
+          <t>13/03/2004</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>06/05/2014</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>75789146</t>
+          <t>60047907</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,20 +3021,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13/03/2004</t>
+          <t>24/05/2006</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>60047907</t>
+          <t>79514651</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3084,30 +3084,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>ROMARIO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24/05/2006</t>
+          <t>29/01/2016</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>05/04/2016</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>79514651</t>
+          <t>91698640</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ROMARIO</t>
+          <t>SAYDA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29/01/2016</t>
+          <t>26/01/2020</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>05/04/2016</t>
+          <t>26/01/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>91698640</t>
+          <t>28591667</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3205,30 +3205,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAYDA</t>
+          <t>AQUILES</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>26/01/2020</t>
+          <t>07/11/1950</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>26/01/2025</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,7 +3258,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28591667</t>
+          <t>79228663</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AQUILES</t>
+          <t>AREM RICARDO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>07/11/1950</t>
+          <t>04/08/2015</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>04/08/2015</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>79228663</t>
+          <t>92611665</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AREM RICARDO</t>
+          <t>ADRIEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>04/08/2015</t>
+          <t>04/11/2021</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>04/08/2015</t>
+          <t>10/01/2023</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>92611665</t>
+          <t>45040747</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ADRIEL</t>
+          <t>NELSON</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>04/11/2021</t>
+          <t>09/05/1988</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>10/01/2023</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>45040747</t>
+          <t>23969574</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>POTOCINO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NELSON</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,11 +3471,11 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>09/05/1988</t>
+          <t>18/04/1973</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>14/02/2012</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23969574</t>
+          <t>49070415</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>POTOCINO</t>
+          <t>VILLAR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/04/1973</t>
+          <t>07/04/1991</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>14/02/2012</t>
+          <t>07/09/2022</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,45 +3573,45 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49070415</t>
+          <t>62269253</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CCENTE</t>
+          <t>CCORIPURI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VILLAR</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>NICOL MELODI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>07/04/1991</t>
+          <t>02/03/2007</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>07/09/2022</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>62269253</t>
+          <t>62094257</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NICOL MELODI</t>
+          <t>QUITLIS SEFER</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>02/03/2007</t>
+          <t>01/02/2010</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>62094257</t>
+          <t>28576582</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>QUITLIS SEFER</t>
+          <t>JUAN ARCADIO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01/02/2010</t>
+          <t>12/01/1969</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28576582</t>
+          <t>28527042</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JUAN ARCADIO</t>
+          <t>ZENOBIA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12/01/1969</t>
+          <t>14/02/1977</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28527042</t>
+          <t>42758477</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,20 +3840,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ZENOBIA</t>
+          <t>EDWIN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>14/02/1977</t>
+          <t>26/10/1984</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42758477</t>
+          <t>45930796</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EDWIN</t>
+          <t>SEBERO EFRIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>26/10/1984</t>
+          <t>01/02/1987</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>45930796</t>
+          <t>60148327</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SEBERO EFRIN</t>
+          <t>JHOAN KENNY</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01/02/1987</t>
+          <t>19/11/2006</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>60148327</t>
+          <t>81392343</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JHOAN KENNY</t>
+          <t>JHINO EYAL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/11/2006</t>
+          <t>20/04/2014</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>25/07/2016</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>81392343</t>
+          <t>91369531</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,30 +4087,30 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JHINO EYAL</t>
+          <t>CAMILA YOSSI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20/04/2014</t>
+          <t>14/06/2019</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>25/07/2016</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,40 +4140,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>91369531</t>
+          <t>48827459</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CCORIPURI</t>
+          <t>CCORIÑAUPA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SERENA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAMILA YOSSI</t>
+          <t>ALCIDES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14/06/2019</t>
+          <t>14/05/1990</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>14/06/2024</t>
+          <t>31/03/2015</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>48827459</t>
+          <t>63322116</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,25 +4218,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ALCIDES</t>
+          <t>AYDEE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14/05/1990</t>
+          <t>30/04/1997</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/03/2015</t>
+          <t>23/03/2020</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>63322116</t>
+          <t>63322082</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SERENA</t>
+          <t>SILVERA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AYDEE</t>
+          <t>ANALI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30/04/1997</t>
+          <t>15/06/2011</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>23/03/2020</t>
+          <t>31/03/2015</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,22 +4329,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63322082</t>
+          <t>77292149</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CCORIÑAUPA</t>
+          <t>CENTENO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SILVERA</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANALI</t>
+          <t>JHESENIA ARASELY</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,16 +4353,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15/06/2011</t>
+          <t>08/03/2006</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/03/2015</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>77292149</t>
+          <t>28529642</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4402,35 +4402,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>PEÑAFIEL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>JHESENIA ARASELY</t>
+          <t>ZOCIMO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>08/03/2006</t>
+          <t>01/04/1969</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>17/09/2020</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,40 +4455,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>28529642</t>
+          <t>91369457</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CENTENO</t>
+          <t>CHACHAYMA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PEÑAFIEL</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ZOCIMO</t>
+          <t>EDITH ABIGAIL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>01/04/1969</t>
+          <t>14/06/2019</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17/09/2020</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>91369457</t>
+          <t>81952232</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CHACHAYMA</t>
+          <t>CHAICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EDITH ABIGAIL</t>
+          <t>MAJHY IMASUMACC</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14/06/2019</t>
+          <t>10/07/2021</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>14/06/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>81952232</t>
+          <t>06940947</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CHAICO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MAJHY IMASUMACC</t>
+          <t>MARTHA SATURNINA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/07/2021</t>
+          <t>19/01/1965</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06940947</t>
+          <t>78251205</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MARTHA SATURNINA</t>
+          <t>ROUS ANALY</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,16 +4668,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/01/1965</t>
+          <t>10/09/2013</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2013</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>78251205</t>
+          <t>60514768</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CHIMAYCO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ROUS ANALY</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10/09/2013</t>
+          <t>17/10/1995</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>30/09/2013</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>60514768</t>
+          <t>60514770</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>MICHAEL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,16 +4794,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17/10/1995</t>
+          <t>14/12/1998</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>60514770</t>
+          <t>60514769</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MICHAEL</t>
+          <t>ROYER</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14/12/1998</t>
+          <t>13/02/2001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>60514769</t>
+          <t>76876687</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4911,20 +4911,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ROYER</t>
+          <t>GLIONILDA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13/02/2001</t>
+          <t>12/09/2004</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>76876687</t>
+          <t>61879286</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GLIONILDA</t>
+          <t>RAQUEL ZARAI</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12/09/2004</t>
+          <t>20/07/2009</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>61879286</t>
+          <t>42948912</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CHIMAYCO</t>
+          <t>CIERTO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RAQUEL ZARAI</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,21 +5046,21 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20/07/2009</t>
+          <t>28/03/1985</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>04/10/2022</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,45 +5085,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42948912</t>
+          <t>28564778</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CIERTO</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>28/03/1985</t>
+          <t>04/05/1954</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>04/10/2022</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28564778</t>
+          <t>28527473</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>04/05/1954</t>
+          <t>10/03/1975</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28527473</t>
+          <t>42420496</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>ABDON</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10/03/1975</t>
+          <t>08/04/1980</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>42420496</t>
+          <t>44951196</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5284,25 +5284,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ABDON</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>08/04/1980</t>
+          <t>15/06/1985</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>44951196</t>
+          <t>44120368</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>RUTH MARIBEL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,11 +5361,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>15/06/1985</t>
+          <t>02/12/1986</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>44120368</t>
+          <t>46291698</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RUTH MARIBEL</t>
+          <t>EDITA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>02/12/1986</t>
+          <t>16/10/1989</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>46291698</t>
+          <t>70918288</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5478,20 +5478,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EDITA</t>
+          <t>HUBER</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>16/10/1989</t>
+          <t>27/02/1993</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>18/10/2018</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>70918288</t>
+          <t>79476788</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5536,35 +5536,35 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>HUBER</t>
+          <t>LUCIA SHERYL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>27/02/1993</t>
+          <t>14/01/2016</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18/10/2018</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>79476788</t>
+          <t>94339353</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LUCIA SHERYL</t>
+          <t>AMBER THAIZ</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14/01/2016</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>94339353</t>
+          <t>70419395</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>JANAMPA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AMBER THAIZ</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>03/04/1992</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>10/07/2018</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>70419395</t>
+          <t>43875546</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JANAMPA</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>BEKY MIRIELA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>03/04/1992</t>
+          <t>02/02/1984</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>10/07/2018</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>43875546</t>
+          <t>76878694</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5788,25 +5788,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BEKY MIRIELA</t>
+          <t>ROY</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>02/02/1984</t>
+          <t>22/04/1995</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>76878694</t>
+          <t>81780144</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ROY</t>
+          <t>JHEFERSON</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,16 +5865,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>22/04/1995</t>
+          <t>22/11/2019</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,35 +5904,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>81780144</t>
+          <t>79436199</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JHEFERSON</t>
+          <t>AZUMI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22/11/2019</t>
+          <t>15/08/2015</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>19/04/2016</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>79436199</t>
+          <t>43252782</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AZUMI</t>
+          <t>ERCILIA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,16 +5991,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>15/08/2015</t>
+          <t>30/10/1985</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>19/04/2016</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>43252782</t>
+          <t>48741177</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6045,20 +6045,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ERCILIA</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>30/10/1985</t>
+          <t>23/12/1990</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>48741177</t>
+          <t>70934022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>MILTON</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,11 +6117,11 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23/12/1990</t>
+          <t>01/09/1995</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>28/08/2012</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>70934022</t>
+          <t>90636443</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6166,30 +6166,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SOLIER</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MILTON</t>
+          <t>AYLEN ITZEL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01/09/1995</t>
+          <t>19/02/2018</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>28/08/2012</t>
+          <t>19/02/2023</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>90636443</t>
+          <t>94447401</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AYLEN ITZEL</t>
+          <t>YARETZI AITHANA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>19/02/2018</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>19/02/2023</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94447401</t>
+          <t>45349083</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>CUSICHE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SOLIER</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>YARETZI AITHANA</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>12/03/1986</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>45349083</t>
+          <t>91595794</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>RONY ANGELO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,21 +6369,21 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>12/03/1986</t>
+          <t>17/11/2019</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,40 +6408,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>91595794</t>
+          <t>28597855</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CUSICHE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>LEANDRO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RONY ANGELO</t>
+          <t>CARMEN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>17/11/2019</t>
+          <t>09/11/1971</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>04/05/2014</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>28597855</t>
+          <t>28278800</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LEANDRO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CARMEN</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>09/11/1971</t>
+          <t>27/07/1968</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>04/05/2014</t>
+          <t>28/06/2013</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,35 +6534,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>28278800</t>
+          <t>47062994</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>PAREJAS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>27/07/1968</t>
+          <t>29/09/1987</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>28/06/2013</t>
+          <t>23/05/2018</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,27 +6597,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>47062994</t>
+          <t>45040752</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PAREJAS</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>JANETH GLADYS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29/09/1987</t>
+          <t>07/09/1987</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>23/05/2018</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>45040752</t>
+          <t>28575953</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6670,25 +6670,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>JANETH GLADYS</t>
+          <t>REYMUNDO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>07/09/1987</t>
+          <t>15/03/1968</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>01/06/2015</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28575953</t>
+          <t>90165979</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>SEDANO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>REYMUNDO</t>
+          <t>LIAM SMITH</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>15/03/1968</t>
+          <t>09/04/2017</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>21/05/2022</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,35 +6786,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>90165979</t>
+          <t>94568193</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SEDANO</t>
+          <t>RIVAS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LIAM SMITH</t>
+          <t>YAMILET SHANTAL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>09/04/2017</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>21/05/2022</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,22 +6849,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>94568193</t>
+          <t>80424659</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>GAVILAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>YAMILET SHANTAL</t>
+          <t>MAXIMINA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>13/04/1970</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>80424659</t>
+          <t>90449180</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GAVILAN</t>
+          <t>ASTUPILLO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MAXIMINA</t>
+          <t>HAIME STELA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>13/04/1970</t>
+          <t>15/10/2017</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>15/10/2022</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,7 +6975,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>90449180</t>
+          <t>91648713</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ASTUPILLO</t>
+          <t>CCENCHO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>HAIME STELA</t>
+          <t>PRISCILA LOURDES</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,11 +6999,11 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>15/10/2017</t>
+          <t>23/12/2019</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>15/10/2022</t>
+          <t>23/12/2024</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>91648713</t>
+          <t>74349616</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7048,30 +7048,30 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CCENCHO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PRISCILA LOURDES</t>
+          <t>JHONATAN</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23/12/2019</t>
+          <t>31/12/1994</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>23/12/2024</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>74349616</t>
+          <t>74349617</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JHONATAN</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>31/12/1994</t>
+          <t>30/11/1996</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>74349617</t>
+          <t>63433394</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>30/11/1996</t>
+          <t>01/02/1999</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>63433394</t>
+          <t>77800813</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>BRICH MILANDER</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>01/02/1999</t>
+          <t>01/11/2003</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>77800813</t>
+          <t>77916546</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7305,20 +7305,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BRICH MILANDER</t>
+          <t>KAREN NATALY</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>01/11/2003</t>
+          <t>10/12/2005</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>77916546</t>
+          <t>60240738</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7368,20 +7368,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>KAREN NATALY</t>
+          <t>KENYO EUSEBIO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>10/12/2005</t>
+          <t>03/11/2007</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>60240738</t>
+          <t>63339068</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KENYO EUSEBIO</t>
+          <t>ALDO ALEXIS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>03/11/2007</t>
+          <t>24/04/2011</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>63339068</t>
+          <t>79413404</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7494,30 +7494,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ALDO ALEXIS</t>
+          <t>SELA NAREEN</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>24/04/2011</t>
+          <t>04/12/2015</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>05/12/2015</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,7 +7542,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>79413404</t>
+          <t>91363295</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SELA NAREEN</t>
+          <t>VALENTINA KAREN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7566,11 +7566,11 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>04/12/2015</t>
+          <t>10/06/2019</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>05/12/2015</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,7 +7605,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>91363295</t>
+          <t>62473413</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7615,30 +7615,30 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VALENTINA KAREN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>10/06/2019</t>
+          <t>16/09/2005</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>10/06/2024</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>62473413</t>
+          <t>81780143</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>SAMAMPO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
+          <t>DEYVI</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>16/09/2005</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>19/11/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,7 +7731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>81780143</t>
+          <t>25008275</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SAMAMPO</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DEYVI</t>
+          <t>EUSEBIO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19/11/2019</t>
+          <t>01/08/1957</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>19/11/2024</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,40 +7794,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>25008275</t>
+          <t>01189752</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>FONSECA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>AQUINO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EUSEBIO</t>
+          <t>ROSALBA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>01/08/1957</t>
+          <t>19/11/1977</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>15/06/2012</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,40 +7857,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01189752</t>
+          <t>91820447</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>GAMBOA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AQUINO</t>
+          <t>ANCCASI</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ROSALBA</t>
+          <t>JAMIR ABDIEL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>19/11/1977</t>
+          <t>19/04/2020</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>15/06/2012</t>
+          <t>19/04/2025</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>91820447</t>
+          <t>46500135</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7930,30 +7930,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ANCCASI</t>
+          <t>CONDORAY</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JAMIR ABDIEL</t>
+          <t>LURGIA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>19/04/2020</t>
+          <t>24/08/1990</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>19/04/2025</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,35 +7983,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>46500135</t>
+          <t>23258707</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CONDORAY</t>
+          <t>HUAMANI</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LURGIA</t>
+          <t>NARCISO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>24/08/1990</t>
+          <t>15/04/1976</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,45 +8046,45 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>23258707</t>
+          <t>91610005</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HUAMANI</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NARCISO</t>
+          <t>ANALY AMARA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>15/04/1976</t>
+          <t>26/11/2019</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,40 +8109,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>91610005</t>
+          <t>41790369</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>SINARAHUA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ANALY AMARA</t>
+          <t>SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>26/11/2019</t>
+          <t>17/03/1982</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>27/05/2015</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,22 +8172,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>41790369</t>
+          <t>48406841</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SINARAHUA</t>
+          <t>JAULIS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SEGUNDO JUAN</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8196,11 +8196,11 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>17/03/1982</t>
+          <t>23/09/1986</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>27/05/2015</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>48406841</t>
+          <t>62227456</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8245,35 +8245,35 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JAULIS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>DARA ROUSE</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23/09/1986</t>
+          <t>22/09/2010</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,35 +8298,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>62227456</t>
+          <t>81583934</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HUALLPA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DARA ROUSE</t>
+          <t>LIAN ANTONIO</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22/09/2010</t>
+          <t>07/05/2014</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>23/09/2018</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,7 +8361,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>81583934</t>
+          <t>91741583</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8376,30 +8376,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LIAN ANTONIO</t>
+          <t>ABIGAIL NAISHA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>07/05/2014</t>
+          <t>22/02/2020</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>23/09/2018</t>
+          <t>22/02/2025</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,7 +8424,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>91741583</t>
+          <t>45768669</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8434,30 +8434,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ABIGAIL NAISHA</t>
+          <t>NELSON</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>22/02/2020</t>
+          <t>21/06/1989</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>22/02/2025</t>
+          <t>20/08/2012</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,35 +8487,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>45768669</t>
+          <t>80091710</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HUALLPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>CAMASI</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NELSON</t>
+          <t>SANTA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>21/06/1989</t>
+          <t>15/08/1976</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>20/08/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>80091710</t>
+          <t>93269447</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CAMASI</t>
+          <t>LUNAZCO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SANTA</t>
+          <t>KHIARA BELEN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,21 +8574,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>15/08/1976</t>
+          <t>18/02/2023</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>13/03/2023</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>93269447</t>
+          <t>91934044</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LUNAZCO</t>
+          <t>MANUELO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>KHIARA BELEN</t>
+          <t>YEIRA ZAMARA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,11 +8637,11 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>18/02/2023</t>
+          <t>04/07/2020</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>13/03/2023</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>91934044</t>
+          <t>94420538</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>YEIRA ZAMARA</t>
+          <t>JAZLIN AITANA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,11 +8700,11 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>04/07/2020</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>94420538</t>
+          <t>28282421</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,35 +8749,35 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MANUELO</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JAZLIN AITANA</t>
+          <t>HUMBERTO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>24/07/1945</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>28282421</t>
+          <t>76088573</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,35 +8812,35 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>HUMBERTO</t>
+          <t>YUDITH</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>24/07/1945</t>
+          <t>01/04/1995</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,7 +8865,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>76088573</t>
+          <t>81623248</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8880,30 +8880,30 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>YUDITH</t>
+          <t>JOSEPH</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>01/04/1995</t>
+          <t>08/04/2015</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/10/2015</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,40 +8928,40 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>81623248</t>
+          <t>28567493</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUILLCA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>JOSEPH</t>
+          <t>ODILIA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>08/04/2015</t>
+          <t>05/10/1965</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>30/10/2015</t>
+          <t>14/09/2011</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,7 +8991,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>28567493</t>
+          <t>28595773</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ODILIA</t>
+          <t>OLGA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>05/10/1965</t>
+          <t>28/12/1968</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>14/09/2011</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>28595773</t>
+          <t>28529650</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OLGA</t>
+          <t>MARUJA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>28/12/1968</t>
+          <t>18/10/1973</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9117,7 +9117,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28529650</t>
+          <t>60148332</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9127,25 +9127,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MARUJA</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>18/10/1973</t>
+          <t>21/11/1994</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>23/09/2018</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,7 +9180,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>60148332</t>
+          <t>62227494</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9195,30 +9195,30 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>MARILY</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>21/11/1994</t>
+          <t>25/08/1997</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>23/09/2018</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>62227494</t>
+          <t>62227253</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MARILY</t>
+          <t>SADITH ANGELA</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>25/08/1997</t>
+          <t>17/05/1999</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9306,45 +9306,45 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>62227253</t>
+          <t>23214772</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HUILLCA</t>
+          <t>HUIZA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SADITH ANGELA</t>
+          <t>ELVES</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>17/05/1999</t>
+          <t>19/10/1974</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9369,22 +9369,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>23214772</t>
+          <t>06167167</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HUIZA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ELVES</t>
+          <t>DIONICIO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19/10/1974</t>
+          <t>08/04/1962</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>28/06/2013</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9432,22 +9432,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>06167167</t>
+          <t>42529614</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DIONICIO</t>
+          <t>LAMARTINO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9456,16 +9456,16 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>08/04/1962</t>
+          <t>17/02/1983</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>28/06/2013</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9495,35 +9495,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>42529614</t>
+          <t>40965309</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LAMARTINO</t>
+          <t>ROSARIO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>17/02/1983</t>
+          <t>09/08/1981</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9558,22 +9558,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>40965309</t>
+          <t>28315335</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>JUSCAMAYTA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>CCORAHUA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ROSARIO</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9582,11 +9582,11 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>09/08/1981</t>
+          <t>22/01/1975</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28315335</t>
+          <t>94206134</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9631,35 +9631,35 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CCORAHUA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>TAYLOR LEONEL</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>22/01/1975</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>94206134</t>
+          <t>76878775</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TAYLOR LEONEL</t>
+          <t>ROY EDILBERTO</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9708,21 +9708,21 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>22/10/1999</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9747,35 +9747,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>76878775</t>
+          <t>91128790</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JUSCAMAYTA</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ROY EDILBERTO</t>
+          <t>BERTA ELOISA</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22/10/1999</t>
+          <t>16/10/2006</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>30/12/2020</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9810,45 +9810,45 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>91128790</t>
+          <t>92880446</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BERTA ELOISA</t>
+          <t>EMIR KENNETH</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>16/10/2006</t>
+          <t>07/05/2022</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>30/12/2020</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9873,22 +9873,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>92880446</t>
+          <t>91045162</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>LIFONCIO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>EMIR KENNETH</t>
+          <t>THIAGO AYRTON</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9897,11 +9897,11 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>07/05/2022</t>
+          <t>10/10/2018</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>10/10/2023</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9936,7 +9936,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>91045162</t>
+          <t>92986471</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>PORMACHI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>THIAGO AYRTON</t>
+          <t>IAN JAZIEL</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>10/10/2018</t>
+          <t>22/07/2022</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>10/10/2023</t>
+          <t>22/09/2022</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9999,22 +9999,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>92986471</t>
+          <t>91595902</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LIFONCIO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PORMACHI</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>IAN JAZIEL</t>
+          <t>ERICK SUNYU</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10023,11 +10023,11 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22/07/2022</t>
+          <t>17/11/2019</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>22/09/2022</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10062,7 +10062,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>91595902</t>
+          <t>41002505</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10072,30 +10072,30 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>ORIHUELA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ERICK SUNYU</t>
+          <t>BASILIA</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>17/11/2019</t>
+          <t>04/04/1976</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10125,22 +10125,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>41002505</t>
+          <t>91606830</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>BASILIA</t>
+          <t>LUANA ESPERANZA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10149,16 +10149,16 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>04/04/1976</t>
+          <t>24/11/2019</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>24/11/2024</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10188,7 +10188,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>91606830</t>
+          <t>70793406</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LUANA ESPERANZA</t>
+          <t>AYDA LUZ</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10212,16 +10212,16 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>24/11/2019</t>
+          <t>10/02/1994</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>24/11/2024</t>
+          <t>10/09/2012</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10251,35 +10251,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>70793406</t>
+          <t>70419413</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AYDA LUZ</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>10/02/1994</t>
+          <t>03/11/1991</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>10/09/2012</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>70419413</t>
+          <t>90739428</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>AXEL GAEL VEKER</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10338,21 +10338,21 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>03/11/1991</t>
+          <t>22/04/2018</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>22/04/2023</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10377,40 +10377,40 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>90739428</t>
+          <t>46743091</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>AXEL GAEL VEKER</t>
+          <t>MARUJA</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22/04/2018</t>
+          <t>29/12/1990</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>22/04/2023</t>
+          <t>30/11/2012</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10440,7 +10440,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>46743091</t>
+          <t>91610034</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ZAMBRANO</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>MARUJA</t>
+          <t>JENNIFER CAMILA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10464,16 +10464,16 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>29/12/1990</t>
+          <t>26/11/2019</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>30/11/2012</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10503,27 +10503,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>91610034</t>
+          <t>91502056</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LUERA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ZAMBRANO</t>
+          <t>CUYA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>JENNIFER CAMILA</t>
+          <t>DERECK CALE</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>26/11/2019</t>
+          <t>15/09/2019</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10566,22 +10566,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>91502056</t>
+          <t>74098389</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUERA</t>
+          <t>LUJAN</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CUYA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DERECK CALE</t>
+          <t>GABRIEL SHEROO</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>15/09/2019</t>
+          <t>19/03/2009</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10629,22 +10629,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>74098389</t>
+          <t>71671966</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUJAN</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>SILVERA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>GABRIEL SHEROO</t>
+          <t>ANGEL JOEL</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10653,21 +10653,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>19/03/2009</t>
+          <t>27/05/2008</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10692,22 +10692,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>71671966</t>
+          <t>94044801</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>LUNASCO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SILVERA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ANGEL JOEL</t>
+          <t>EITAN MATEO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>27/05/2008</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10755,35 +10755,35 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>94044801</t>
+          <t>91387361</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUNASCO</t>
+          <t>MADUEÑO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EITAN MATEO</t>
+          <t>LUZ JHANDIRA</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>26/06/2019</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>26/06/2024</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10818,40 +10818,40 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>91387361</t>
+          <t>40796044</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MADUEÑO</t>
+          <t>MALLMA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LUZ JHANDIRA</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>26/06/2019</t>
+          <t>19/04/1980</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>26/06/2024</t>
+          <t>21/10/2011</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10881,7 +10881,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>40796044</t>
+          <t>60240717</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>POTOSINO</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>JUAN ANDREE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19/04/1980</t>
+          <t>15/06/2007</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10944,7 +10944,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>60240717</t>
+          <t>28586274</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>POTOSINO</t>
+          <t>VICAÑA</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>JUAN ANDREE</t>
+          <t>NICANOR</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>15/06/2007</t>
+          <t>10/01/1961</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>21/10/2011</t>
+          <t>03/11/2011</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11007,22 +11007,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>28586274</t>
+          <t>28586517</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MALLMA</t>
+          <t>MALLQUI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VICAÑA</t>
+          <t>CRESPO</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NICANOR</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11031,11 +11031,11 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>10/01/1961</t>
+          <t>15/07/1952</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>03/11/2011</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11070,45 +11070,45 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>28586517</t>
+          <t>93204094</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MALLQUI</t>
+          <t>MAMANI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CRESPO</t>
+          <t>POTOSINO</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>SOFIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>15/07/1952</t>
+          <t>03/01/2023</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/07/2023</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11133,45 +11133,45 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>93204094</t>
+          <t>48366775</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MAMANI</t>
+          <t>MANUELO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>POTOSINO</t>
+          <t>JULIAN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SOFIA ALEJANDRA</t>
+          <t>ELVIS MAYCO</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>03/01/2023</t>
+          <t>07/10/1993</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>03/07/2023</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11196,7 +11196,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>48366775</t>
+          <t>80713430</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11206,35 +11206,35 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>JULIAN</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ELVIS MAYCO</t>
+          <t>ALEJANDRA JIMENA</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>07/10/1993</t>
+          <t>24/08/2012</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>23/04/2021</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11259,22 +11259,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>80713430</t>
+          <t>61578090</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MANUELO</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CIERTO</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ALEJANDRA JIMENA</t>
+          <t>ANYELA YESMILINDA</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11283,11 +11283,11 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>24/08/2012</t>
+          <t>22/02/2010</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>23/04/2021</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11322,7 +11322,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>61578090</t>
+          <t>81227078</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11337,20 +11337,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ANYELA YESMILINDA</t>
+          <t>MIULLER NEYMAR</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>22/02/2010</t>
+          <t>20/05/2013</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>81227078</t>
+          <t>42635312</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CIERTO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>MIULLER NEYMAR</t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11409,16 +11409,16 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20/05/2013</t>
+          <t>05/01/1983</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>21/10/2022</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11448,7 +11448,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>42635312</t>
+          <t>42811694</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>QUINTIMARI</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t>CORNELIO MEUJAEL</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11472,11 +11472,11 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>05/01/1983</t>
+          <t>20/01/1985</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>21/10/2022</t>
+          <t>06/04/2015</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11511,45 +11511,45 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>42811694</t>
+          <t>60658354</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>QUINTIMARI</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CORNELIO MEUJAEL</t>
+          <t>EDITH SOLANCH</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20/01/1985</t>
+          <t>01/11/2007</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>06/04/2015</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11574,22 +11574,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>60658354</t>
+          <t>41037974</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SINCHITULLO</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>EDITH SOLANCH</t>
+          <t>NORA ENMA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11598,21 +11598,21 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>01/11/2007</t>
+          <t>01/07/1981</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11637,35 +11637,35 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>41037974</t>
+          <t>46542581</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SINCHITULLO</t>
+          <t>CAYETANO</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NORA ENMA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>01/07/1981</t>
+          <t>30/11/1986</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11700,7 +11700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>46542581</t>
+          <t>62227255</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11724,16 +11724,16 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>30/11/1986</t>
+          <t>08/09/1998</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11763,7 +11763,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>62227255</t>
+          <t>60537115</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CAYETANO</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>JOSEPH ELEOSSER</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11787,11 +11787,11 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>08/09/1998</t>
+          <t>24/07/2007</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>60537115</t>
+          <t>93524537</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>JOSEPH ELEOSSER</t>
+          <t>JHANDIEL ENZO</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11850,21 +11850,21 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>24/07/2007</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>93524537</t>
+          <t>93717006</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11899,25 +11899,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>VICAÑA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>JHANDIEL ENZO</t>
+          <t>KORAL ITSAYANA</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>10/02/2024</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>01/09/2023</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11952,22 +11952,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>93717006</t>
+          <t>28587451</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VICAÑA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>KORAL ITSAYANA</t>
+          <t>NANCIA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11976,21 +11976,21 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>10/02/2024</t>
+          <t>12/04/1968</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>08/05/2024</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12015,22 +12015,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>28587451</t>
+          <t>28570376</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NANCIA</t>
+          <t>MERCEDES TOMASA</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12039,21 +12039,21 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>12/04/1968</t>
+          <t>24/12/1944</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12078,40 +12078,40 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>28570376</t>
+          <t>42110156</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>OBREGON</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MERCEDES TOMASA</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>24/12/1944</t>
+          <t>13/07/1981</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12141,7 +12141,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>42110156</t>
+          <t>70325895</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>FELIMON ABRAHAM</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12165,11 +12165,11 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>13/07/1981</t>
+          <t>15/04/1989</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>08/09/2012</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>70325895</t>
+          <t>78027451</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12214,35 +12214,35 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>LIMACHE</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>FELIMON ABRAHAM</t>
+          <t>SAMMY</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>15/04/1989</t>
+          <t>04/02/2013</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>08/09/2012</t>
+          <t>27/05/2015</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>78027451</t>
+          <t>79603222</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12282,30 +12282,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SAMMY</t>
+          <t>ERICK YANDEL</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>04/02/2013</t>
+          <t>04/04/2016</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>27/05/2015</t>
+          <t>04/04/2016</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12330,7 +12330,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>79603222</t>
+          <t>93229578</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ERICK YANDEL</t>
+          <t>GAEL LUDWIN</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12354,11 +12354,11 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>04/04/2016</t>
+          <t>21/01/2023</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>04/04/2016</t>
+          <t>21/01/2023</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12393,22 +12393,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>93229578</t>
+          <t>28563981</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OBREGON</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LIMACHE</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>GAEL LUDWIN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12417,21 +12417,21 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>21/01/2023</t>
+          <t>18/01/1965</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>21/01/2023</t>
+          <t>06/10/2011</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>28563981</t>
+          <t>60514862</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12466,35 +12466,35 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>SERENA</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>MIRIAN</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>18/01/1965</t>
+          <t>16/03/2004</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12519,45 +12519,45 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>60514862</t>
+          <t>47365956</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SERENA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>MIRIAN</t>
+          <t>NOE GABRIEL</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>16/03/2004</t>
+          <t>03/04/1984</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>06/10/2011</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12582,7 +12582,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>47365956</t>
+          <t>77352851</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12592,12 +12592,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NOE GABRIEL</t>
+          <t>GABRIEL URBANO</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12606,16 +12606,16 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>03/04/1984</t>
+          <t>26/03/2001</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12645,7 +12645,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>77352851</t>
+          <t>76876706</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>GABRIEL URBANO</t>
+          <t>KERVIN EDWARD</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12669,11 +12669,11 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>26/03/2001</t>
+          <t>18/04/2003</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>76876706</t>
+          <t>76874672</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>KERVIN EDWARD</t>
+          <t>JUNIOR DEYVIS</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12732,11 +12732,11 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>18/04/2003</t>
+          <t>19/06/2005</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12771,7 +12771,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>76874672</t>
+          <t>62473415</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12786,25 +12786,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>JUNIOR DEYVIS</t>
+          <t>YUREMA</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>19/06/2005</t>
+          <t>16/01/2009</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>03/12/2012</t>
+          <t>21/02/2012</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12834,7 +12834,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>62473415</t>
+          <t>63322117</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>YUREMA</t>
+          <t>YUNGA ZAURI</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12858,11 +12858,11 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>16/01/2009</t>
+          <t>26/08/2011</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>21/02/2012</t>
+          <t>03/12/2012</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12897,40 +12897,40 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>63322117</t>
+          <t>76254509</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>YUNGA ZAURI</t>
+          <t>JOSE ANDRES</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>26/08/2011</t>
+          <t>31/05/2005</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
